--- a/config/CalSim3DeliveryDataExtractionInitFile_v3.xlsx
+++ b/config/CalSim3DeliveryDataExtractionInitFile_v3.xlsx
@@ -1,21 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dino\COEQWAL\COEQWAL_GIT\COEQWAL_V3\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{366EF92F-27FB-4DA0-80A9-AEA0A92D861B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEE531A0-7360-41C0-B4AD-9E0DA8A26005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12000" yWindow="210" windowWidth="13785" windowHeight="18390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Init" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -193,9 +204,6 @@
     <t>A2</t>
   </si>
   <si>
-    <t>O47</t>
-  </si>
-  <si>
     <t>Inflows Extraction Dir</t>
   </si>
   <si>
@@ -226,25 +234,28 @@
     <t>coeqwal_cs3_scenario_listing_v7.xlsx</t>
   </si>
   <si>
-    <t>A101</t>
-  </si>
-  <si>
-    <t>B101</t>
-  </si>
-  <si>
-    <t>C101</t>
-  </si>
-  <si>
-    <t>G101</t>
-  </si>
-  <si>
-    <t>H101</t>
-  </si>
-  <si>
-    <t>I101</t>
-  </si>
-  <si>
-    <t>J101</t>
+    <t>O476</t>
+  </si>
+  <si>
+    <t>A117</t>
+  </si>
+  <si>
+    <t>B117</t>
+  </si>
+  <si>
+    <t>C117</t>
+  </si>
+  <si>
+    <t>G117</t>
+  </si>
+  <si>
+    <t>H117</t>
+  </si>
+  <si>
+    <t>I117</t>
+  </si>
+  <si>
+    <t>J117</t>
   </si>
 </sst>
 </file>
@@ -619,7 +630,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -840,7 +851,7 @@
         <v>56</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="E22" t="s">
         <v>45</v>
@@ -848,10 +859,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="E23" t="s">
         <v>45</v>
@@ -859,10 +870,10 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="E24" t="s">
         <v>45</v>
@@ -870,10 +881,10 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="E25" t="s">
         <v>45</v>
@@ -884,13 +895,13 @@
         <v>54</v>
       </c>
       <c r="B26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="E26" t="s">
         <v>45</v>

--- a/config/CalSim3DeliveryDataExtractionInitFile_v3.xlsx
+++ b/config/CalSim3DeliveryDataExtractionInitFile_v3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dino\COEQWAL\COEQWAL_GIT\COEQWAL_V3\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEE531A0-7360-41C0-B4AD-9E0DA8A26005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42F96B9A-1E62-4EB4-8510-3BFA92D09A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12000" yWindow="210" windowWidth="13785" windowHeight="18390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2685" yWindow="2685" windowWidth="18540" windowHeight="18645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Init" sheetId="1" r:id="rId1"/>
@@ -153,9 +153,6 @@
     <t>D8</t>
   </si>
   <si>
-    <t>E266</t>
-  </si>
-  <si>
     <t>Data Extraction Dir</t>
   </si>
   <si>
@@ -256,6 +253,9 @@
   </si>
   <si>
     <t>J117</t>
+  </si>
+  <si>
+    <t>E267</t>
   </si>
 </sst>
 </file>
@@ -630,7 +630,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -652,7 +652,7 @@
         <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -666,7 +666,7 @@
         <v>15</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -680,7 +680,7 @@
         <v>18</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -694,7 +694,7 @@
         <v>21</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -708,7 +708,7 @@
         <v>24</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -722,7 +722,7 @@
         <v>27</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -736,7 +736,7 @@
         <v>30</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -774,137 +774,137 @@
         <v>39</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="E17" t="s">
         <v>44</v>
-      </c>
-      <c r="E17" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="E18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="E20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="E21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" t="s">
         <v>54</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="D22" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="E23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="E24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="E25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B26" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="E26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
